--- a/penumbra_tests/xlsx/files/pivot_header.xlsx
+++ b/penumbra_tests/xlsx/files/pivot_header.xlsx
@@ -22,7 +22,7 @@
     <t>Data retrieved on: September 4, 2026, 3:12 PM. 42 rows</t>
   </si>
   <si>
-    <t>Search filter: Engineering</t>
+    <t>Filter: Engineering</t>
   </si>
   <si>
     <t>Imported: awards.csv (120 rows): Sep 1, 2026, 8:00 AM</t>
